--- a/education_surveys/023_graduate_curriculum_relevance_questionnaire--education_surveys.xlsx
+++ b/education_surveys/023_graduate_curriculum_relevance_questionnaire--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,10 +440,10 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,90 +538,86 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>curriculum_category</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>What category does the graduate curriculum belong to?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Select a category</t>
-        </is>
-      </c>
+          <t>Describe the graduate curriculum's relevance to education surveys.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>curriculum_templates</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Which category does the graduate curriculum relate to?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>curriculum_relevance_rating</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>How would you rate the graduate curriculum's relevance to education surveys?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Would you recommend using the graduate curriculum for education surveys?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -668,7 +664,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
@@ -693,7 +689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>curriculum_category_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -710,7 +706,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>curriculum_category_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -727,7 +723,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>curriculum_templates_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,7 +740,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>curriculum_templates_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -761,34 +757,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>education-surveys</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>education-surveys</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>questionnaire-templates</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>questionnaire-templates</t>
+          <t>False</t>
         </is>
       </c>
     </row>
